--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126366186</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126366259</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>126365777</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>126366636</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>126366362</v>
       </c>
       <c r="B7" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>126366872</v>
       </c>
       <c r="B8" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>126366595</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126366186</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126366259</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57859-2024 artfynd.xlsx
+++ b/artfynd/A 57859-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126366186</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126366259</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
